--- a/report.xlsx
+++ b/report.xlsx
@@ -413,54 +413,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Leaves</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Salary Level</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bob</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rejected</t>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>David</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
